--- a/Luban/Config/Datas/Levels/L30/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L30/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L30 W1/25; N=60; EHP=406.560000; normal:17x30,normal:18x30</t>
+          <t>L30 W1/25; N=60; EHP=1136.517307; normal:17x30,normal:18x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L30 W2/25; N=66; EHP=468.279874; normal:17x33,normal:18x33</t>
+          <t>L30 W2/25; N=66; EHP=1309.051999; normal:17x33,normal:18x33 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10021940,10021942,10049219,10021940,10021942,10049219,10021940,10021942,10049220,10021940,10021942,10049220,10021940,10021942,10049221,10021940,10021942,10049221,10021940,10021942,10049222,10021940,10021942,10049222,10021940,10021942,10049223,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021940,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941</t>
+          <t>10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021942,10021940,10021940,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021941,10021940,10021940,10021940,10021940,10021940,10021940,10021940,10021940,10021940</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L30 W3/25; N=72; EHP=566.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x1,normal:17x22,normal:18x21,swarm:84x20</t>
+          <t>L30 W3/25; N=72; EHP=1712.648276; normal:17x31,normal:18x21,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10021943,10021945,10049224,10021943,10021945,10049224,10021943,10021945,10049225,10021943,10021945,10049225,10021943,10021945,10049226,10021943,10021945,10049227,10021943,10021945,10049227,10021943,10021945,10049228,10021943,10021945,10049228,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021943,10021943,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944</t>
+          <t>10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021945,10021943,10021943,10021943,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021944,10021943,10021943,10021943,10021943,10021943,10021943,10021943,10021943,10021943</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L30 W4/25; N=78; EHP=708.000000; air:2x2,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x24,normal:18x24,swarm:84x21</t>
+          <t>L30 W4/25; N=78; EHP=2128.293213; normal:17x33,normal:18x24,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10021946,10021949,10049229,10021948,10021946,10021949,10049229,10021948,10021946,10021949,10049230,10021948,10021946,10021949,10049230,10021948,10021946,10021949,10049231,10021950,10021946,10021949,10049231,10021950,10021946,10021949,10049232,10021950,10021946,10021949,10049232,10021950,10021946,10021949,10049233,10021951,10021946,10021949,10049233,10021951,10021946,10021949,10021951,10021946,10021949,10021951,10021946,10021949,10021946,10021949,10021946,10021949,10021946,10021949,10021946,10021949,10021946,10021949,10021946,10021949,10021946,10021949,10021947,10021949,10021947,10021949,10021947,10021949,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947</t>
+          <t>10021946,10049229,10049229,10021948,10021946,10049229,10049229,10021948,10021946,10049230,10049230,10021948,10021946,10049230,10049230,10021948,10021946,10049231,10049231,10021950,10021946,10049231,10049231,10021950,10021946,10049232,10049232,10021950,10021946,10049232,10049232,10021950,10021946,10049233,10049233,10021951,10021946,10049233,10049233,10021951,10021946,10021949,10021951,10021946,10021949,10021951,10021946,10021949,10021946,10021949,10021946,10021949,10021946,10021949,10021946,10021949,10021946,10021949,10021946,10021949,10021946,10021949,10021947,10021949,10021947,10021949,10021947,10021949,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947,10021947</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L30 W5/25; N=84; EHP=1318.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x20,normal:18x19,medium:83x4,swarm:84x23,medium:108x4,medium:123x4</t>
+          <t>L30 W5/25; N=84; EHP=3731.127060; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x4,medium:108x4,medium:123x4,normal:17x20,normal:18x19,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>10021955,10021961,10021957,10049234,10021960,10021955,10021961,10021957,10049234,10021960,10021955,10021961,10021957,10021952,10021960,10021955,10021961,10021958,10021952,10021960,10021955,10021961,10021958,10021952,10021960,10021955,10021961,10021959,10049235,10021963,10021955,10021961,10021959,10049235,10021963,10021955,10021961,10021962,10021953,10021963,10021955,10021961,10021962,10021953,10021963,10021955,10021961,10021962,10021954,10021964,10021955,10021961,10021954,10021964,10021955,10021961,10021964,10021955,10021961,10021964,10021955,10021961,10021955,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021956,10021956,10021956,10021956,10021956</t>
+          <t>10021955,10049234,10021957,10049234,10021960,10021955,10049234,10021957,10049234,10021960,10021955,10021952,10021957,10021952,10021960,10021955,10021952,10021958,10021952,10021960,10021955,10021952,10021958,10021952,10021960,10021955,10049235,10021959,10049235,10021963,10021955,10049235,10021959,10049235,10021963,10021955,10021953,10021962,10021953,10021963,10021955,10021953,10021962,10021953,10021963,10021955,10021954,10021962,10021954,10021964,10021955,10021954,10021954,10021964,10021955,10021961,10021964,10021955,10021961,10021964,10021955,10021961,10021955,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021961,10021956,10021956,10021956,10021956,10021956,10021956</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L30 W6/25; N=90; EHP=1345.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x16,fast:30x3,fast:58x2,fast:64x2,medium:83x5,swarm:84x25,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L30 W6/25; N=90; EHP=3809.827516; air:2x4,air:11x6,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x2,fast:98x3,medium:83x5,medium:108x4,medium:123x4,normal:17x15,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>10021968,10021974,10021970,10049236,10021973,10021968,10021974,10021970,10049236,10021973,10021968,10021974,10021971,10021965,10021973,10021968,10021974,10021971,10021965,10021973,10021968,10021974,10021971,10049237,10021976,10021968,10021974,10021972,10049237,10021976,10021968,10021974,10021972,10049237,10021976,10021968,10021974,10021972,10021966,10021976,10021968,10021974,10021975,10021966,10021976,10021968,10021974,10021975,10021967,10021977,10021968,10021974,10021975,10021967,10021977,10021968,10021974,10021967,10021977,10021968,10021974,10021977,10021968,10021974,10021977,10021968,10021974,10021968,10021974,10021968,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021969,10021969,10021969,10021969,10021969,10021969</t>
+          <t>10021968,10049236,10021970,10049236,10021973,10021968,10049236,10021970,10049236,10021973,10021968,10021965,10021971,10021965,10021973,10021968,10021965,10021971,10021965,10021973,10021968,10049237,10021971,10049237,10021976,10021968,10049237,10021972,10049237,10021976,10021968,10049237,10021972,10049237,10021976,10021968,10021966,10021972,10021966,10021976,10021968,10021966,10021975,10021966,10021976,10021968,10021967,10021975,10021967,10021977,10021968,10021967,10021975,10021967,10021977,10021968,10021967,10021967,10021977,10021968,10021974,10021977,10021968,10021974,10021977,10021968,10021974,10021968,10021974,10021968,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021974,10021969,10021969,10021969,10021969,10021969,10021969,10021969</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L30 W7/25; N=96; EHP=1508.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x17,normal:18x16,fast:30x2,fast:58x3,fast:64x3,medium:83x4,swarm:84x26,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L30 W7/25; N=96; EHP=4272.727579; air:2x4,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x2,fast:58x3,fast:64x3,fast:98x3,medium:83x4,medium:108x5,medium:123x5,normal:17x17,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>10021981,10021987,10021983,10049238,10021986,10021981,10021987,10021983,10049238,10021986,10021981,10021987,10021983,10049238,10021986,10021981,10021987,10021984,10021978,10021986,10021981,10021987,10021984,10021978,10021986,10021981,10021987,10021984,10049239,10021989,10021981,10021987,10021985,10049239,10021989,10021981,10021987,10021985,10049239,10021989,10021981,10021987,10021985,10021979,10021989,10021981,10021987,10021988,10021979,10021989,10021981,10021987,10021988,10021980,10021990,10021981,10021987,10021988,10021980,10021990,10021981,10021987,10021990,10021981,10021987,10021990,10021981,10021987,10021990,10021981,10021987,10021981,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021982,10021982,10021982,10021982,10021982,10021982</t>
+          <t>10021981,10049238,10021983,10049238,10021986,10021981,10049238,10021983,10049238,10021986,10021981,10049238,10021983,10049238,10021986,10021981,10021978,10021984,10021978,10021986,10021981,10021978,10021984,10021978,10021986,10021981,10049239,10021984,10049239,10021989,10021981,10049239,10021985,10049239,10021989,10021981,10049239,10021985,10049239,10021989,10021981,10021979,10021985,10021979,10021989,10021981,10021979,10021988,10021979,10021989,10021981,10021980,10021988,10021980,10021990,10021981,10021980,10021988,10021980,10021990,10021981,10021987,10021990,10021981,10021987,10021990,10021981,10021987,10021990,10021981,10021987,10021981,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021987,10021982,10021982,10021982,10021982,10021982,10021982,10021982</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L30 W8/25; N=102; EHP=1937.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x17,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L30 W8/25; N=102; EHP=5483.687597; air:2x6,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x17,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>10021994,10022000,10021996,10049240,10021999,10021994,10022000,10021996,10049240,10021999,10021994,10022000,10021996,10049240,10021999,10021994,10022000,10021997,10021991,10021999,10021994,10022000,10021997,10021991,10021999,10021994,10022000,10021997,10021991,10021999,10021994,10022000,10021998,10049241,10022002,10021994,10022000,10021998,10049241,10022002,10021994,10022000,10021998,10021992,10022002,10021994,10022000,10022001,10021992,10022002,10021994,10022000,10022001,10021992,10022002,10021994,10022000,10022001,10021993,10022003,10021994,10022000,10021993,10022003,10021994,10022000,10022003,10021994,10022000,10022003,10021994,10022000,10022003,10021994,10022000,10021994,10022000,10021994,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10021995,10021995,10021995,10021995,10021995,10021995</t>
+          <t>10021994,10049240,10021996,10049240,10021999,10021994,10049240,10021996,10049240,10021999,10021994,10049240,10021996,10049240,10021999,10021994,10021991,10021997,10021991,10021999,10021994,10021991,10021997,10021991,10021999,10021994,10021991,10021997,10021991,10021999,10021994,10049241,10021998,10049241,10022002,10021994,10049241,10021998,10049241,10022002,10021994,10021992,10021998,10021992,10022002,10021994,10021992,10022001,10021992,10022002,10021994,10021992,10022001,10021992,10022002,10021994,10021993,10022001,10021993,10022003,10021994,10021993,10021993,10022003,10021994,10022000,10022003,10021994,10022000,10022003,10021994,10022000,10022003,10021994,10022000,10021994,10022000,10021994,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10022000,10021995,10021995,10021995,10021995,10021995,10021995,10021995</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L30 W9/25; N=108; EHP=2470.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x19,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x6,swarm:84x30,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L30 W9/25; N=108; EHP=6994.743163; air:2x6,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x6,medium:108x5,medium:123x5,normal:17x19,normal:18x18,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>10022007,10022013,10022009,10049242,10022012,10022007,10022013,10022009,10049242,10022012,10022007,10022013,10022009,10022004,10022012,10022007,10022013,10022009,10022004,10022012,10022007,10022013,10022010,10022004,10022012,10022007,10022013,10022010,10049243,10022015,10022007,10022013,10022010,10049243,10022015,10022007,10022013,10022011,10049243,10022015,10022007,10022013,10022011,10022005,10022015,10022007,10022013,10022011,10022005,10022015,10022007,10022013,10022014,10022005,10022015,10022007,10022013,10022014,10022006,10022016,10022007,10022013,10022014,10022006,10022016,10022007,10022013,10022006,10022016,10022007,10022013,10022016,10022007,10022013,10022016,10022007,10022013,10022016,10022007,10022013,10022007,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022008,10022008,10022008,10022008,10022008,10022008,10022008</t>
+          <t>10022007,10049242,10022009,10049242,10022012,10022007,10049242,10022009,10049242,10022012,10022007,10022004,10022009,10022004,10022012,10022007,10022004,10022009,10022004,10022012,10022007,10022004,10022010,10022004,10022012,10022007,10049243,10022010,10049243,10022015,10022007,10049243,10022010,10049243,10022015,10022007,10049243,10022011,10049243,10022015,10022007,10022005,10022011,10022005,10022015,10022007,10022005,10022011,10022005,10022015,10022007,10022005,10022014,10022005,10022015,10022007,10022006,10022014,10022006,10022016,10022007,10022006,10022014,10022006,10022016,10022007,10022006,10022006,10022016,10022007,10022013,10022016,10022007,10022013,10022016,10022007,10022013,10022016,10022007,10022013,10022007,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022013,10022008,10022008,10022008,10022008,10022008,10022008,10022008,10022008</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L30 W10/25; N=114; EHP=4551.000000; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x19,normal:18x20,fast:30x4,fast:58x3,fast:64x3,medium:83x5,swarm:84x31,fast:98x3,medium:108x6,medium:123x6</t>
+          <t>L30 W10/25; N=114; EHP=12891.067517; air:2x4,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x6,medium:123x6,normal:17x19,normal:18x20,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>10022017,10022027,10022019,10049244,10022026,10022020,10022017,10022027,10022019,10049244,10022026,10022020,10022017,10022027,10022019,10049244,10022026,10022021,10022017,10022027,10022022,10049245,10022026,10022021,10022017,10022027,10022022,10049245,10022026,10045327,10022017,10022027,10022022,10049245,10022026,10022024,10022017,10022027,10022022,10049246,10022030,10022025,10022017,10022027,10022023,10049246,10022030,10022025,10022017,10022027,10022023,10049246,10022030,10022028,10022017,10022027,10022023,10049247,10022030,10022028,10022017,10022027,10022029,10049247,10022030,10045328,10022017,10022027,10022029,10049248,10022030,10022032,10022017,10022027,10022029,10049248,10022031,10022017,10022027,10022029,10049248,10022031,10022017,10022027,10022031,10022018,10022027,10022031,10022018,10022027,10022031,10022018,10022027,10022031,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022027,10022027,10022027,10022027</t>
+          <t>10022017,10049244,10022019,10049244,10022026,10022020,10022017,10049244,10022019,10049244,10022026,10022020,10022017,10049244,10022019,10049244,10022026,10022021,10022017,10049245,10022022,10049245,10022026,10022021,10022017,10049245,10022022,10049245,10022026,10045327,10022017,10049245,10022022,10049245,10022026,10022024,10022017,10049246,10022022,10049246,10022030,10022025,10022017,10049246,10022023,10049246,10022030,10022025,10022017,10049246,10022023,10049246,10022030,10022028,10022017,10049247,10022023,10049247,10022030,10022028,10022017,10049247,10022029,10049247,10022030,10045328,10022017,10049248,10022029,10049248,10022030,10022032,10022017,10049248,10022029,10049248,10022031,10022017,10049248,10022029,10049248,10022031,10022017,10022027,10022031,10022018,10022027,10022031,10022018,10022027,10022031,10022018,10022027,10022031,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022018,10022027,10022027,10022027,10022027,10022027</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L30 W11/25; N=120; EHP=4643.000000; air:2x3,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x15,normal:18x14,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x33,heavy:86x2,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L30 W11/25; N=120; EHP=13123.880457; air:2x6,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x14,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>10022036,10022046,10022038,10049249,10022045,10022039,10022036,10022046,10022038,10049249,10022045,10022039,10022036,10022046,10022038,10049249,10022045,10022040,10022036,10022046,10022038,10022033,10022045,10022040,10022036,10022046,10022041,10022033,10022045,10022043,10022036,10022046,10022041,10022033,10022045,10022044,10022036,10022046,10022041,10049250,10022049,10045329,10022036,10022046,10022041,10049250,10022049,10022047,10022036,10022046,10022042,10049250,10022049,10022047,10022036,10022046,10022042,10022034,10022049,10045330,10022036,10022046,10022042,10022034,10022049,10022051,10022036,10022046,10022042,10022034,10022049,10022051,10022036,10022046,10022048,10022035,10022050,10022036,10022046,10022048,10022035,10022050,10022036,10022046,10022048,10022035,10022050,10022037,10022046,10022050,10022037,10022046,10022050,10022037,10022046,10022050,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022046,10022046,10022046,10022046</t>
+          <t>10022036,10049249,10022038,10049249,10022045,10022039,10022036,10049249,10022038,10049249,10022045,10022039,10022036,10049249,10022038,10049249,10022045,10022040,10022036,10022033,10022038,10022033,10022045,10022040,10022036,10022033,10022041,10022033,10022045,10022043,10022036,10022033,10022041,10022033,10022045,10022044,10022036,10049250,10022041,10049250,10022049,10045329,10022036,10049250,10022041,10049250,10022049,10022047,10022036,10049250,10022042,10049250,10022049,10022047,10022036,10022034,10022042,10022034,10022049,10045330,10022036,10022034,10022042,10022034,10022049,10022051,10022036,10022034,10022042,10022034,10022049,10022051,10022036,10022035,10022048,10022035,10022050,10022036,10022035,10022048,10022035,10022050,10022036,10022035,10022048,10022035,10022050,10022037,10022046,10022050,10022037,10022046,10022050,10022037,10022046,10022050,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022037,10022046,10022046,10022046,10022046,10022046</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L30 W12/25; N=126; EHP=4803.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x6,swarm:84x35,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L30 W12/25; N=126; EHP=13581.160581; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>10022055,10022066,10022057,10049251,10022065,10022058,10022055,10022066,10022057,10049251,10022065,10022058,10022055,10022066,10022057,10049251,10022065,10022059,10022055,10022066,10022057,10022052,10022065,10022059,10022055,10022066,10022060,10022052,10022065,10022062,10022055,10022066,10022060,10022052,10022065,10022062,10022055,10022066,10022060,10049252,10022069,10022063,10022055,10022066,10022061,10049252,10022069,10022063,10022055,10022066,10022061,10049252,10022069,10022064,10022055,10022066,10022061,10049252,10022069,10045331,10022055,10022066,10022061,10022053,10022069,10022067,10022055,10022066,10022068,10022053,10022069,10022071,10022055,10022066,10022068,10022053,10022070,10022071,10022055,10022066,10022068,10022054,10022070,10022055,10022066,10022068,10022054,10022070,10022055,10022066,10022054,10022070,10022055,10022066,10022070,10022056,10022066,10022070,10022056,10022066,10022070,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022066,10022066,10022066</t>
+          <t>10022055,10049251,10022057,10049251,10022065,10022058,10022055,10049251,10022057,10049251,10022065,10022058,10022055,10049251,10022057,10049251,10022065,10022059,10022055,10022052,10022057,10022052,10022065,10022059,10022055,10022052,10022060,10022052,10022065,10022062,10022055,10022052,10022060,10022052,10022065,10022062,10022055,10049252,10022060,10049252,10022069,10022063,10022055,10049252,10022061,10049252,10022069,10022063,10022055,10049252,10022061,10049252,10022069,10022064,10022055,10049252,10022061,10049252,10022069,10045331,10022055,10022053,10022061,10022053,10022069,10022067,10022055,10022053,10022068,10022053,10022069,10022071,10022055,10022053,10022068,10022053,10022070,10022071,10022055,10022054,10022068,10022054,10022070,10022055,10022054,10022068,10022054,10022070,10022055,10022054,10022054,10022070,10022055,10022066,10022070,10022056,10022066,10022070,10022056,10022066,10022070,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022056,10022066,10022066,10022066,10022066</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L30 W13/25; N=132; EHP=5857.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x17,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x36,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x7,heavy:127x2</t>
+          <t>L30 W13/25; N=132; EHP=16563.806970; air:2x6,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x7,normal:17x17,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>10022075,10022085,10022077,10049253,10022084,10045332,10022075,10022085,10022077,10049253,10022084,10022078,10022075,10022085,10022077,10049253,10022084,10022078,10022075,10022085,10022077,10049253,10022084,10022081,10022075,10022085,10022079,10022072,10022084,10022081,10022075,10022085,10022079,10022072,10022084,10022082,10022075,10022085,10022079,10022072,10022084,10022082,10022075,10022085,10022079,10049254,10022089,10022083,10022075,10022085,10022080,10049254,10022089,10022086,10022075,10022085,10022080,10049254,10022089,10022087,10022075,10022085,10022080,10022073,10022089,10022087,10022075,10022085,10022080,10022073,10022089,10022091,10022075,10022085,10022088,10022073,10022089,10022091,10022075,10022085,10022088,10022073,10022089,10022075,10022085,10022088,10022074,10022090,10022075,10022085,10022088,10022074,10022090,10022075,10022085,10022074,10022090,10022076,10022085,10022090,10022076,10022085,10022090,10022076,10022085,10022090,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022085,10022085,10022085,10022085</t>
+          <t>10022075,10049253,10022077,10049253,10022084,10045332,10022075,10049253,10022077,10049253,10022084,10022078,10022075,10049253,10022077,10049253,10022084,10022078,10022075,10049253,10022077,10049253,10022084,10022081,10022075,10022072,10022079,10022072,10022084,10022081,10022075,10022072,10022079,10022072,10022084,10022082,10022075,10022072,10022079,10022072,10022084,10022082,10022075,10049254,10022079,10049254,10022089,10022083,10022075,10049254,10022080,10049254,10022089,10022086,10022075,10049254,10022080,10049254,10022089,10022087,10022075,10022073,10022080,10022073,10022089,10022087,10022075,10022073,10022080,10022073,10022089,10022091,10022075,10022073,10022088,10022073,10022089,10022091,10022075,10022073,10022088,10022073,10022089,10022075,10022074,10022088,10022074,10022090,10022075,10022074,10022088,10022074,10022090,10022075,10022074,10022074,10022090,10022076,10022085,10022090,10022076,10022085,10022090,10022076,10022085,10022090,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022076,10022085,10022085,10022085,10022085,10022085</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L30 W14/25; N=138; EHP=7064.000000; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x17,normal:18x17,fast:30x4,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x38,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L30 W14/25; N=138; EHP=19982.540252; air:2x8,air:11x6,air:12x6,air:13x8,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x6,normal:17x17,normal:18x17,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>10022095,10022106,10022097,10049255,10022105,10022098,10022101,10022095,10022106,10022097,10049255,10022105,10045333,10022095,10022106,10022097,10049255,10022105,10022102,10022095,10022106,10022097,10022092,10022105,10022102,10022095,10022106,10022099,10022092,10022105,10022103,10022095,10022106,10022099,10022092,10022105,10022103,10022095,10022106,10022099,10022092,10022105,10022104,10022095,10022106,10022099,10049256,10022110,10022104,10022095,10022106,10022100,10049256,10022110,10022107,10022095,10022106,10022100,10049256,10022110,10022107,10022095,10022106,10022100,10022093,10022110,10022108,10022095,10022106,10022100,10022093,10022110,10022108,10022095,10022106,10022109,10022093,10022110,10022112,10022095,10022106,10022109,10022093,10022110,10022112,10022095,10022106,10022109,10022094,10022111,10022095,10022106,10022109,10022094,10022111,10022095,10022106,10022109,10022094,10022111,10022096,10022106,10022111,10022096,10022106,10022111,10022096,10022106,10022111,10022096,10022106,10022111,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022106,10022106,10022106,10022106,10022106,10022106</t>
+          <t>10022095,10049255,10022097,10049255,10022105,10022098,10022101,10022095,10049255,10022097,10049255,10022105,10045333,10022095,10049255,10022097,10049255,10022105,10022102,10022095,10022092,10022097,10022092,10022105,10022102,10022095,10022092,10022099,10022092,10022105,10022103,10022095,10022092,10022099,10022092,10022105,10022103,10022095,10022092,10022099,10022092,10022105,10022104,10022095,10049256,10022099,10049256,10022110,10022104,10022095,10049256,10022100,10049256,10022110,10022107,10022095,10049256,10022100,10049256,10022110,10022107,10022095,10022093,10022100,10022093,10022110,10022108,10022095,10022093,10022100,10022093,10022110,10022108,10022095,10022093,10022109,10022093,10022110,10022112,10022095,10022093,10022109,10022093,10022110,10022112,10022095,10022094,10022109,10022094,10022111,10022095,10022094,10022109,10022094,10022111,10022095,10022094,10022109,10022094,10022111,10022096,10022106,10022111,10022096,10022106,10022111,10022096,10022106,10022111,10022096,10022106,10022111,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022096,10022106,10022106,10022106,10022106,10022106,10022106,10022106</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L30 W15/25; N=144; EHP=12326.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x17,normal:18x17,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x2,fast:98x5,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L30 W15/25; N=144; EHP=34838.544880; air:2x6,air:11x8,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x5,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10022113,10022124,10022115,10049257,10022123,10022116,10022113,10022124,10022115,10049257,10022123,10022116,10022113,10022124,10022115,10049257,10022123,10022117,10022113,10022124,10022115,10049258,10022123,10022117,10022113,10022124,10022118,10049258,10022123,10022120,10022113,10022124,10022118,10049258,10022123,10022120,10022113,10022124,10022118,10049258,10022123,10022121,10022113,10022124,10022118,10049259,10022128,10022121,10022113,10022124,10022118,10049259,10022128,10022122,10022113,10022124,10022119,10049259,10022128,10022122,10022113,10022124,10022119,10049259,10022128,10022125,10022113,10022124,10022119,10049260,10022128,10022125,10022113,10022124,10022119,10049260,10022128,10022126,10022113,10022124,10022119,10049260,10022128,10022126,10022113,10022124,10022127,10049261,10022129,10045334,10022113,10022124,10022127,10049261,10022129,10022113,10022124,10022127,10049261,10022129,10022114,10022124,10022127,10049261,10022129,10022114,10022124,10022129,10022114,10022124,10022129,10022114,10022124,10022129,10022114,10022124,10022129,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022124,10022124,10022124,10022124,10022124,10022124,10022124</t>
+          <t>10022113,10049257,10022115,10049257,10022123,10022116,10022113,10049257,10022115,10049257,10022123,10022116,10022113,10049257,10022115,10049257,10022123,10022117,10022113,10049258,10022115,10049258,10022123,10022117,10022113,10049258,10022118,10049258,10022123,10022120,10022113,10049258,10022118,10049258,10022123,10022120,10022113,10049258,10022118,10049258,10022123,10022121,10022113,10049259,10022118,10049259,10022128,10022121,10022113,10049259,10022118,10049259,10022128,10022122,10022113,10049259,10022119,10049259,10022128,10022122,10022113,10049259,10022119,10049259,10022128,10022125,10022113,10049260,10022119,10049260,10022128,10022125,10022113,10049260,10022119,10049260,10022128,10022126,10022113,10049260,10022119,10049260,10022128,10022126,10022113,10049261,10022127,10049261,10022129,10045334,10022113,10049261,10022127,10049261,10022129,10022113,10049261,10022127,10049261,10022129,10022114,10049261,10022127,10049261,10022129,10022114,10022124,10022129,10022114,10022124,10022129,10022114,10022124,10022129,10022114,10022124,10022129,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022114,10022124,10022124,10022124,10022124,10022124,10022124,10022124,10022124</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L30 W16/25; N=150; EHP=12573.000000; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x17,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x42,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x8,heavy:127x1</t>
+          <t>L30 W16/25; N=150; EHP=35552.451138; air:2x6,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x7,medium:123x8,normal:17x17,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10022133,10022143,10022135,10049262,10022142,10022136,10022133,10022143,10022135,10049262,10022142,10022136,10022133,10022143,10022135,10049262,10022142,10022137,10022133,10022143,10022135,10049262,10022142,10022137,10022133,10022143,10022135,10022130,10022142,10022140,10022133,10022143,10022138,10022130,10022142,10022140,10022133,10022143,10022138,10022130,10022142,10045335,10022133,10022143,10022138,10049263,10022142,10022141,10022133,10022143,10022138,10049263,10022147,10022141,10022133,10022143,10022139,10049263,10022147,10022144,10022133,10022143,10022139,10049263,10022147,10022144,10022133,10022143,10022139,10022131,10022147,10022145,10022133,10022143,10022139,10022131,10022147,10022145,10022133,10022143,10022139,10022131,10022147,10022149,10022133,10022143,10022146,10022131,10022147,10022149,10022133,10022143,10022146,10022132,10022147,10022133,10022143,10022146,10022132,10022148,10022133,10022143,10022146,10022132,10022148,10022133,10022143,10022132,10022148,10022134,10022143,10022148,10022134,10022143,10022148,10022134,10022143,10022148,10022134,10022143,10022148,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022143,10022143,10022143,10022143,10022143</t>
+          <t>10022133,10049262,10022135,10049262,10022142,10022136,10022133,10049262,10022135,10049262,10022142,10022136,10022133,10049262,10022135,10049262,10022142,10022137,10022133,10049262,10022135,10049262,10022142,10022137,10022133,10022130,10022135,10022130,10022142,10022140,10022133,10022130,10022138,10022130,10022142,10022140,10022133,10022130,10022138,10022130,10022142,10045335,10022133,10049263,10022138,10049263,10022142,10022141,10022133,10049263,10022138,10049263,10022147,10022141,10022133,10049263,10022139,10049263,10022147,10022144,10022133,10049263,10022139,10049263,10022147,10022144,10022133,10022131,10022139,10022131,10022147,10022145,10022133,10022131,10022139,10022131,10022147,10022145,10022133,10022131,10022139,10022131,10022147,10022149,10022133,10022131,10022146,10022131,10022147,10022149,10022133,10022132,10022146,10022132,10022147,10022133,10022132,10022146,10022132,10022148,10022133,10022132,10022146,10022132,10022148,10022133,10022132,10022132,10022148,10022134,10022143,10022148,10022134,10022143,10022148,10022134,10022143,10022148,10022134,10022143,10022148,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022134,10022143,10022143,10022143,10022143,10022143,10022143</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L30 W17/25; N=156; EHP=12825.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x8,swarm:84x43,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L30 W17/25; N=156; EHP=36272.361255; air:2x8,air:11x6,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x7,normal:17x19,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10022153,10022164,10022155,10049264,10022163,10022156,10022153,10022164,10022155,10049264,10022163,10022156,10022153,10022164,10022155,10049264,10022163,10022157,10022153,10022164,10022155,10049264,10022163,10022157,10022153,10022164,10022155,10022150,10022163,10022160,10022153,10022164,10022158,10022150,10022163,10022160,10022153,10022164,10022158,10022150,10022163,10022161,10022153,10022164,10022158,10022150,10022163,10022161,10022153,10022164,10022158,10049265,10022168,10022162,10022153,10022164,10022158,10049265,10022168,10022162,10022153,10022164,10022159,10049265,10022168,10022165,10022153,10022164,10022159,10049265,10022168,10022165,10022153,10022164,10022159,10022151,10022168,10022166,10022153,10022164,10022159,10022151,10022168,10022166,10022153,10022164,10022167,10022151,10022168,10022170,10022153,10022164,10022167,10022151,10022168,10022170,10022153,10022164,10022167,10022152,10022169,10022153,10022164,10022167,10022152,10022169,10022153,10022164,10022167,10022152,10022169,10022154,10022164,10022169,10022154,10022164,10022169,10022154,10022164,10022169,10022154,10022164,10022169,10022154,10022164,10022169,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022164,10022164,10022164,10022164,10022164,10022164</t>
+          <t>10022153,10049264,10022155,10049264,10022163,10022156,10022153,10049264,10022155,10049264,10022163,10022156,10022153,10049264,10022155,10049264,10022163,10022157,10022153,10049264,10022155,10049264,10022163,10022157,10022153,10022150,10022155,10022150,10022163,10022160,10022153,10022150,10022158,10022150,10022163,10022160,10022153,10022150,10022158,10022150,10022163,10022161,10022153,10022150,10022158,10022150,10022163,10022161,10022153,10049265,10022158,10049265,10022168,10022162,10022153,10049265,10022158,10049265,10022168,10022162,10022153,10049265,10022159,10049265,10022168,10022165,10022153,10049265,10022159,10049265,10022168,10022165,10022153,10022151,10022159,10022151,10022168,10022166,10022153,10022151,10022159,10022151,10022168,10022166,10022153,10022151,10022167,10022151,10022168,10022170,10022153,10022151,10022167,10022151,10022168,10022170,10022153,10022152,10022167,10022152,10022169,10022153,10022152,10022167,10022152,10022169,10022153,10022152,10022167,10022152,10022169,10022154,10022164,10022169,10022154,10022164,10022169,10022154,10022164,10022169,10022154,10022164,10022169,10022154,10022164,10022169,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022154,10022164,10022164,10022164,10022164,10022164,10022164,10022164</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L30 W18/25; N=162; EHP=13702.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x3,normal:17x19,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L30 W18/25; N=162; EHP=38733.982849; air:2x8,air:11x8,air:12x8,air:13x8,air:14x6,fast:30x5,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10022174,10022185,10022176,10049266,10022184,10022177,10022174,10022185,10022176,10049266,10022184,10022177,10022174,10022185,10022176,10049266,10022184,10022178,10022174,10022185,10022176,10049266,10022184,10022178,10022174,10022185,10022176,10022171,10022184,10022181,10022174,10022185,10022179,10022171,10022184,10022181,10022174,10022185,10022179,10022171,10022184,10022182,10022174,10022185,10022179,10022171,10022184,10022182,10022174,10022185,10022179,10049267,10022189,10022183,10022174,10022185,10022179,10049267,10022189,10022183,10022174,10022185,10022180,10049267,10022189,10022186,10022174,10022185,10022180,10049267,10022189,10022186,10022174,10022185,10022180,10022172,10022189,10022187,10022174,10022185,10022180,10022172,10022189,10022187,10022174,10022185,10022180,10022172,10022189,10022191,10022174,10022185,10022188,10022172,10022189,10022191,10022174,10022185,10022188,10022173,10022190,10022174,10022185,10022188,10022173,10022190,10022174,10022185,10022188,10022173,10022190,10022174,10022185,10022188,10022173,10022190,10022175,10022185,10022190,10022175,10022185,10022190,10022175,10022185,10022190,10022175,10022185,10022190,10022175,10022185,10022190,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022185,10022185,10022185,10022185,10022185,10022185,10022185</t>
+          <t>10022174,10049266,10022176,10049266,10022184,10022177,10022174,10049266,10022176,10049266,10022184,10022177,10022174,10049266,10022176,10049266,10022184,10022178,10022174,10049266,10022176,10049266,10022184,10022178,10022174,10022171,10022176,10022171,10022184,10022181,10022174,10022171,10022179,10022171,10022184,10022181,10022174,10022171,10022179,10022171,10022184,10022182,10022174,10022171,10022179,10022171,10022184,10022182,10022174,10049267,10022179,10049267,10022189,10022183,10022174,10049267,10022179,10049267,10022189,10022183,10022174,10049267,10022180,10049267,10022189,10022186,10022174,10049267,10022180,10049267,10022189,10022186,10022174,10022172,10022180,10022172,10022189,10022187,10022174,10022172,10022180,10022172,10022189,10022187,10022174,10022172,10022180,10022172,10022189,10022191,10022174,10022172,10022188,10022172,10022189,10022191,10022174,10022173,10022188,10022173,10022190,10022174,10022173,10022188,10022173,10022190,10022174,10022173,10022188,10022173,10022190,10022174,10022173,10022188,10022173,10022190,10022175,10022185,10022190,10022175,10022185,10022190,10022175,10022185,10022190,10022175,10022185,10022190,10022175,10022185,10022190,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022175,10022185,10022185,10022185,10022185,10022185,10022185,10022185,10022185</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L30 W19/25; N=168; EHP=15871.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L30 W19/25; N=168; EHP=44875.782686; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x9,normal:17x20,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10022195,10022207,10022197,10049268,10022206,10022198,10022202,10022195,10022207,10022197,10049268,10022206,10022198,10022195,10022207,10022197,10049268,10022206,10022199,10022195,10022207,10022197,10049268,10022206,10022199,10022195,10022207,10022197,10022192,10022206,10022203,10022195,10022207,10022200,10022192,10022206,10022203,10022195,10022207,10022200,10022192,10022206,10022204,10022195,10022207,10022200,10022192,10022206,10022204,10022195,10022207,10022200,10049269,10022206,10022205,10022195,10022207,10022200,10049269,10022211,10022205,10022195,10022207,10022201,10049269,10022211,10022208,10022195,10022207,10022201,10049269,10022211,10022208,10022195,10022207,10022201,10022193,10022211,10022208,10022195,10022207,10022201,10022193,10022211,10022209,10022195,10022207,10022201,10022193,10022211,10022209,10022195,10022207,10022210,10022193,10022211,10022213,10022195,10022207,10022210,10022193,10022211,10022213,10022195,10022207,10022210,10022194,10022211,10022195,10022207,10022210,10022194,10022212,10022195,10022207,10022210,10022194,10022212,10022196,10022207,10022194,10022212,10022196,10022207,10022212,10022196,10022207,10022212,10022196,10022207,10022212,10022196,10022207,10022212,10022196,10022207,10022212,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022207,10022207,10022207,10022207,10022207,10022207,10022207</t>
+          <t>10022195,10049268,10022197,10049268,10022206,10022198,10022202,10022195,10049268,10022197,10049268,10022206,10022198,10022195,10049268,10022197,10049268,10022206,10022199,10022195,10049268,10022197,10049268,10022206,10022199,10022195,10022192,10022197,10022192,10022206,10022203,10022195,10022192,10022200,10022192,10022206,10022203,10022195,10022192,10022200,10022192,10022206,10022204,10022195,10022192,10022200,10022192,10022206,10022204,10022195,10049269,10022200,10049269,10022206,10022205,10022195,10049269,10022200,10049269,10022211,10022205,10022195,10049269,10022201,10049269,10022211,10022208,10022195,10049269,10022201,10049269,10022211,10022208,10022195,10022193,10022201,10022193,10022211,10022208,10022195,10022193,10022201,10022193,10022211,10022209,10022195,10022193,10022201,10022193,10022211,10022209,10022195,10022193,10022210,10022193,10022211,10022213,10022195,10022193,10022210,10022193,10022211,10022213,10022195,10022194,10022210,10022194,10022211,10022195,10022194,10022210,10022194,10022212,10022195,10022194,10022210,10022194,10022212,10022196,10022194,10022194,10022212,10022196,10022207,10022212,10022196,10022207,10022212,10022196,10022207,10022212,10022196,10022207,10022212,10022196,10022207,10022212,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022196,10022207,10022207,10022207,10022207,10022207,10022207,10022207,10022207</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L30 W20/25; N=174; EHP=26634.000000; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x20,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x48,heavy:86x3,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L30 W20/25; N=174; EHP=75298.884614; air:2x8,air:11x8,air:12x8,air:13x10,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x8,normal:17x20,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10022217,10022228,10022219,10049270,10022227,10022220,10022217,10022228,10022219,10049270,10022227,10022220,10022217,10022228,10022219,10049270,10022227,10022220,10022217,10022228,10022219,10049270,10022227,10022221,10022217,10022228,10022219,10022214,10022227,10022221,10022217,10022228,10022222,10022214,10022227,10022221,10022217,10022228,10022222,10022214,10022227,10022224,10022217,10022228,10022222,10022214,10022227,10022224,10022217,10022228,10022222,10022214,10022227,10022225,10022217,10022228,10022222,10049271,10022232,10022225,10022217,10022228,10022223,10049271,10022232,10022226,10022217,10022228,10022223,10049271,10022232,10022226,10022217,10022228,10022223,10049271,10022232,10022229,10022217,10022228,10022223,10022215,10022232,10022229,10022217,10022228,10022223,10022215,10022232,10022230,10022217,10022228,10022223,10022215,10022232,10022230,10022217,10022228,10022231,10022215,10022232,10022234,10022217,10022228,10022231,10022216,10022232,10022234,10022217,10022228,10022231,10022216,10022233,10022217,10022228,10022231,10022216,10022233,10022217,10022228,10022231,10022216,10022233,10022218,10022228,10022216,10022233,10022218,10022228,10022233,10022218,10022228,10022233,10022218,10022228,10022233,10022218,10022228,10022233,10022218,10022228,10022233,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022228,10022228,10022228,10022228,10022228,10022228,10022228,10022228</t>
+          <t>10022217,10049270,10022219,10049270,10022227,10022220,10022217,10049270,10022219,10049270,10022227,10022220,10022217,10049270,10022219,10049270,10022227,10022220,10022217,10049270,10022219,10049270,10022227,10022221,10022217,10022214,10022219,10022214,10022227,10022221,10022217,10022214,10022222,10022214,10022227,10022221,10022217,10022214,10022222,10022214,10022227,10022224,10022217,10022214,10022222,10022214,10022227,10022224,10022217,10022214,10022222,10022214,10022227,10022225,10022217,10049271,10022222,10049271,10022232,10022225,10022217,10049271,10022223,10049271,10022232,10022226,10022217,10049271,10022223,10049271,10022232,10022226,10022217,10049271,10022223,10049271,10022232,10022229,10022217,10022215,10022223,10022215,10022232,10022229,10022217,10022215,10022223,10022215,10022232,10022230,10022217,10022215,10022223,10022215,10022232,10022230,10022217,10022215,10022231,10022215,10022232,10022234,10022217,10022216,10022231,10022216,10022232,10022234,10022217,10022216,10022231,10022216,10022233,10022217,10022216,10022231,10022216,10022233,10022217,10022216,10022231,10022216,10022233,10022218,10022216,10022216,10022233,10022218,10022228,10022233,10022218,10022228,10022233,10022218,10022228,10022233,10022218,10022228,10022233,10022218,10022228,10022233,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022218,10022228,10022228,10022228,10022228,10022228,10022228,10022228,10022228,10022228</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L30 W21/25; N=180; EHP=27167.000000; air:2x4,air:11x5,air:12x4,air:13x4,air:14x5,normal:17x21,normal:18x21,fast:30x5,heavy:31x3,heavy:40x3,fast:58x5,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L30 W21/25; N=180; EHP=76833.822625; air:2x8,air:11x10,air:12x8,air:13x8,air:14x10,fast:30x5,fast:58x5,fast:64x6,fast:98x5,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x21,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10022238,10022249,10022240,10049272,10022248,10022241,10022238,10022249,10022240,10049272,10022248,10022241,10022238,10022249,10022240,10049272,10022248,10022242,10022238,10022249,10022240,10049272,10022248,10022242,10022238,10022249,10022240,10022235,10022248,10022242,10022238,10022249,10022240,10022235,10022248,10022245,10022238,10022249,10022243,10022235,10022248,10022245,10022238,10022249,10022243,10022235,10022248,10022246,10022238,10022249,10022243,10049273,10022248,10022246,10022238,10022249,10022243,10049273,10022253,10022247,10022238,10022249,10022243,10049273,10022253,10022247,10022238,10022249,10022244,10049273,10022253,10022250,10022238,10022249,10022244,10049273,10022253,10022250,10022238,10022249,10022244,10022236,10022253,10022251,10022238,10022249,10022244,10022236,10022253,10022251,10022238,10022249,10022244,10022236,10022253,10022255,10022238,10022249,10022252,10022236,10022253,10022255,10022238,10022249,10022252,10022237,10022253,10022255,10022238,10022249,10022252,10022237,10022254,10022238,10022249,10022252,10022237,10022254,10022238,10022249,10022252,10022237,10022254,10022238,10022249,10022252,10022237,10022254,10022239,10022249,10022254,10022239,10022249,10022254,10022239,10022249,10022254,10022239,10022249,10022254,10022239,10022249,10022254,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022249,10022249,10022249,10022249,10022249,10022249,10022249</t>
+          <t>10022238,10049272,10022240,10049272,10022248,10022241,10022238,10049272,10022240,10049272,10022248,10022241,10022238,10049272,10022240,10049272,10022248,10022242,10022238,10049272,10022240,10049272,10022248,10022242,10022238,10022235,10022240,10022235,10022248,10022242,10022238,10022235,10022240,10022235,10022248,10022245,10022238,10022235,10022243,10022235,10022248,10022245,10022238,10022235,10022243,10022235,10022248,10022246,10022238,10049273,10022243,10049273,10022248,10022246,10022238,10049273,10022243,10049273,10022253,10022247,10022238,10049273,10022243,10049273,10022253,10022247,10022238,10049273,10022244,10049273,10022253,10022250,10022238,10049273,10022244,10049273,10022253,10022250,10022238,10022236,10022244,10022236,10022253,10022251,10022238,10022236,10022244,10022236,10022253,10022251,10022238,10022236,10022244,10022236,10022253,10022255,10022238,10022236,10022252,10022236,10022253,10022255,10022238,10022237,10022252,10022237,10022253,10022255,10022238,10022237,10022252,10022237,10022254,10022238,10022237,10022252,10022237,10022254,10022238,10022237,10022252,10022237,10022254,10022238,10022237,10022252,10022237,10022254,10022239,10022249,10022254,10022239,10022249,10022254,10022239,10022249,10022254,10022239,10022249,10022254,10022239,10022249,10022254,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022239,10022249,10022249,10022249,10022249,10022249,10022249,10022249,10022249</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L30 W22/25; N=186; EHP=27711.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x5,normal:17x22,normal:18x23,fast:30x6,heavy:31x2,heavy:40x3,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x52,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x9,heavy:127x3</t>
+          <t>L30 W22/25; N=186; EHP=78348.131902; air:2x8,air:11x8,air:12x10,air:13x8,air:14x10,fast:30x6,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x23,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10022259,10022270,10022261,10049274,10022269,10022262,10022259,10022270,10022261,10049274,10022269,10022262,10022259,10022270,10022261,10049274,10022269,10022263,10022259,10022270,10022261,10049274,10022269,10022263,10022259,10022270,10022261,10049274,10022269,10022266,10022259,10022270,10022264,10022256,10022269,10022266,10022259,10022270,10022264,10022256,10022269,10022266,10022259,10022270,10022264,10022256,10022269,10022267,10022259,10022270,10022264,10022256,10022269,10022267,10022259,10022270,10022264,10049275,10022274,10022267,10022259,10022270,10022264,10049275,10022274,10022268,10022259,10022270,10022265,10049275,10022274,10022268,10022259,10022270,10022265,10049275,10022274,10022271,10022259,10022270,10022265,10049275,10022274,10022271,10022259,10022270,10022265,10022257,10022274,10022272,10022259,10022270,10022265,10022257,10022274,10022272,10022259,10022270,10022265,10022257,10022274,10022276,10022259,10022270,10022273,10022257,10022274,10022276,10022259,10022270,10022273,10022257,10022274,10022276,10022259,10022270,10022273,10022258,10022275,10022259,10022270,10022273,10022258,10022275,10022259,10022270,10022273,10022258,10022275,10022259,10022270,10022273,10022258,10022275,10022260,10022270,10022275,10022260,10022270,10022275,10022260,10022270,10022275,10022260,10022270,10022275,10022260,10022270,10022275,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022270,10022270,10022270,10022270,10022270,10022270,10022270</t>
+          <t>10022259,10049274,10022261,10049274,10022269,10022262,10022259,10049274,10022261,10049274,10022269,10022262,10022259,10049274,10022261,10049274,10022269,10022263,10022259,10049274,10022261,10049274,10022269,10022263,10022259,10049274,10022261,10049274,10022269,10022266,10022259,10022256,10022264,10022256,10022269,10022266,10022259,10022256,10022264,10022256,10022269,10022266,10022259,10022256,10022264,10022256,10022269,10022267,10022259,10022256,10022264,10022256,10022269,10022267,10022259,10049275,10022264,10049275,10022274,10022267,10022259,10049275,10022264,10049275,10022274,10022268,10022259,10049275,10022265,10049275,10022274,10022268,10022259,10049275,10022265,10049275,10022274,10022271,10022259,10049275,10022265,10049275,10022274,10022271,10022259,10022257,10022265,10022257,10022274,10022272,10022259,10022257,10022265,10022257,10022274,10022272,10022259,10022257,10022265,10022257,10022274,10022276,10022259,10022257,10022273,10022257,10022274,10022276,10022259,10022257,10022273,10022257,10022274,10022276,10022259,10022258,10022273,10022258,10022275,10022259,10022258,10022273,10022258,10022275,10022259,10022258,10022273,10022258,10022275,10022259,10022258,10022273,10022258,10022275,10022260,10022270,10022275,10022260,10022270,10022275,10022260,10022270,10022275,10022260,10022270,10022275,10022260,10022270,10022275,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022260,10022270,10022270,10022270,10022270,10022270,10022270,10022270,10022270</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L30 W23/25; N=192; EHP=28266.000000; air:2x5,air:11x4,air:12x5,air:13x5,air:14x4,normal:17x23,normal:18x23,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x53,heavy:86x2,heavy:88x2,fast:98x6,medium:108x10,medium:123x9,heavy:127x3</t>
+          <t>L30 W23/25; N=192; EHP=79925.953704; air:2x10,air:11x8,air:12x10,air:13x10,air:14x8,fast:30x5,fast:58x6,fast:64x6,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x10,medium:123x9,normal:17x23,normal:18x23,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10022280,10022291,10022282,10049276,10022290,10022283,10022280,10022291,10022282,10049276,10022290,10022283,10022280,10022291,10022282,10049276,10022290,10022284,10022280,10022291,10022282,10049276,10022290,10022284,10022280,10022291,10022282,10049276,10022290,10022287,10022280,10022291,10022282,10022277,10022290,10022287,10022280,10022291,10022285,10022277,10022290,10022287,10022280,10022291,10022285,10022277,10022290,10022288,10022280,10022291,10022285,10022277,10022290,10022288,10022280,10022291,10022285,10022277,10022290,10022288,10022280,10022291,10022285,10049277,10022295,10022289,10022280,10022291,10022285,10049277,10022295,10022289,10022280,10022291,10022286,10049277,10022295,10022292,10022280,10022291,10022286,10049277,10022295,10022292,10022280,10022291,10022286,10022278,10022295,10022293,10022280,10022291,10022286,10022278,10022295,10022293,10022280,10022291,10022286,10022278,10022295,10022293,10022280,10022291,10022286,10022278,10022295,10022297,10022280,10022291,10022294,10022278,10022295,10022297,10022280,10022291,10022294,10022279,10022296,10022280,10022291,10022294,10022279,10022296,10022280,10022291,10022294,10022279,10022296,10022280,10022291,10022294,10022279,10022296,10022280,10022291,10022279,10022296,10022281,10022291,10022296,10022281,10022291,10022296,10022281,10022291,10022296,10022281,10022291,10022296,10022281,10022291,10022296,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022291,10022291,10022291,10022291,10022291,10022291,10022291</t>
+          <t>10022280,10049276,10022282,10049276,10022290,10022283,10022280,10049276,10022282,10049276,10022290,10022283,10022280,10049276,10022282,10049276,10022290,10022284,10022280,10049276,10022282,10049276,10022290,10022284,10022280,10049276,10022282,10049276,10022290,10022287,10022280,10022277,10022282,10022277,10022290,10022287,10022280,10022277,10022285,10022277,10022290,10022287,10022280,10022277,10022285,10022277,10022290,10022288,10022280,10022277,10022285,10022277,10022290,10022288,10022280,10022277,10022285,10022277,10022290,10022288,10022280,10049277,10022285,10049277,10022295,10022289,10022280,10049277,10022285,10049277,10022295,10022289,10022280,10049277,10022286,10049277,10022295,10022292,10022280,10049277,10022286,10049277,10022295,10022292,10022280,10022278,10022286,10022278,10022295,10022293,10022280,10022278,10022286,10022278,10022295,10022293,10022280,10022278,10022286,10022278,10022295,10022293,10022280,10022278,10022286,10022278,10022295,10022297,10022280,10022278,10022294,10022278,10022295,10022297,10022280,10022279,10022294,10022279,10022296,10022280,10022279,10022294,10022279,10022296,10022280,10022279,10022294,10022279,10022296,10022280,10022279,10022294,10022279,10022296,10022280,10022279,10022279,10022296,10022281,10022291,10022296,10022281,10022291,10022296,10022281,10022291,10022296,10022281,10022291,10022296,10022281,10022291,10022296,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022281,10022291,10022291,10022291,10022291,10022291,10022291,10022291,10022291</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L30 W24/25; N=198; EHP=30268.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x24,normal:18x24,fast:30x6,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x10,swarm:84x55,heavy:86x2,heavy:88x3,fast:98x5,medium:108x9,medium:123x10,heavy:127x2</t>
+          <t>L30 W24/25; N=198; EHP=85602.238916; air:2x10,air:11x10,air:12x8,air:13x10,air:14x10,fast:30x6,fast:58x6,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x10,medium:108x9,medium:123x10,normal:17x24,normal:18x24,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10022301,10022312,10022303,10049278,10022311,10022304,10022319,10022301,10022312,10022303,10049278,10022311,10022304,10022301,10022312,10022303,10049278,10022311,10022305,10022301,10022312,10022303,10049278,10022311,10022305,10022301,10022312,10022303,10022298,10022311,10022308,10022301,10022312,10022303,10022298,10022311,10022308,10022301,10022312,10022306,10022298,10022311,10022308,10022301,10022312,10022306,10022298,10022311,10022309,10022301,10022312,10022306,10022298,10022311,10022309,10022301,10022312,10022306,10049279,10022311,10022310,10022301,10022312,10022306,10049279,10022316,10022310,10022301,10022312,10022306,10049279,10022316,10022310,10022301,10022312,10022307,10049279,10022316,10022313,10022301,10022312,10022307,10049279,10022316,10022313,10022301,10022312,10022307,10022299,10022316,10022313,10022301,10022312,10022307,10022299,10022316,10022314,10022301,10022312,10022307,10022299,10022316,10022314,10022301,10022312,10022307,10022299,10022316,10022314,10022301,10022312,10022315,10022299,10022316,10022318,10022301,10022312,10022315,10022300,10022316,10022318,10022301,10022312,10022315,10022300,10022317,10022301,10022312,10022315,10022300,10022317,10022301,10022312,10022315,10022300,10022317,10022301,10022312,10022315,10022300,10022317,10022302,10022312,10022317,10022302,10022312,10022317,10022302,10022312,10022317,10022302,10022312,10022317,10022302,10022312,10022317,10022302,10022312,10022317,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022312,10022312,10022312,10022312,10022312,10022312,10022312,10022312,10022312</t>
+          <t>10022301,10049278,10022303,10049278,10022311,10022304,10022319,10022301,10049278,10022303,10049278,10022311,10022304,10022301,10049278,10022303,10049278,10022311,10022305,10022301,10049278,10022303,10049278,10022311,10022305,10022301,10022298,10022303,10022298,10022311,10022308,10022301,10022298,10022303,10022298,10022311,10022308,10022301,10022298,10022306,10022298,10022311,10022308,10022301,10022298,10022306,10022298,10022311,10022309,10022301,10022298,10022306,10022298,10022311,10022309,10022301,10049279,10022306,10049279,10022311,10022310,10022301,10049279,10022306,10049279,10022316,10022310,10022301,10049279,10022306,10049279,10022316,10022310,10022301,10049279,10022307,10049279,10022316,10022313,10022301,10049279,10022307,10049279,10022316,10022313,10022301,10022299,10022307,10022299,10022316,10022313,10022301,10022299,10022307,10022299,10022316,10022314,10022301,10022299,10022307,10022299,10022316,10022314,10022301,10022299,10022307,10022299,10022316,10022314,10022301,10022299,10022315,10022299,10022316,10022318,10022301,10022300,10022315,10022300,10022316,10022318,10022301,10022300,10022315,10022300,10022317,10022301,10022300,10022315,10022300,10022317,10022301,10022300,10022315,10022300,10022317,10022301,10022300,10022315,10022300,10022317,10022302,10022312,10022317,10022302,10022312,10022317,10022302,10022312,10022317,10022302,10022312,10022317,10022302,10022312,10022317,10022302,10022312,10022317,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022302,10022312,10022312,10022312,10022312,10022312,10022312,10022312,10022312,10022312,10022312</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L30 W25/25; N=204; EHP=60407.000000; air:2x4,air:11x5,air:12x5,air:13x5,air:14x5,normal:17x24,normal:18x24,fast:30x6,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x2,heavy:80x3,medium:83x10,swarm:84x57,heavy:86x3,heavy:88x3,fast:98x6,medium:108x10,medium:123x10,heavy:127x2,boss:132x1</t>
+          <t>L30 W25/25; N=204; EHP=170738.727014; air:2x8,air:11x10,air:12x10,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x6,fast:64x6,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x3,heavy:127x2,medium:83x10,medium:108x10,medium:123x10,normal:17x24,normal:18x24,swarm:84x33 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L30/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L30/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>222</v>
+        <v>380</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>208</v>
+        <v>300</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>201</v>
+        <v>390</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>187</v>
+        <v>320</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>173</v>
+        <v>390</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>166</v>
+        <v>320</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>152</v>
+        <v>330</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>145</v>
+        <v>310</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>138</v>
+        <v>390</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>131</v>
+        <v>310</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
